--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486438_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486438_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8845</v>
+        <v>6.3232</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1569</v>
+        <v>5.0272</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7276</v>
+        <v>1.296</v>
       </c>
       <c r="G2" t="n">
         <v>1.9679</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4163</v>
+        <v>0.855</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4747</v>
+        <v>0.3449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9416</v>
+        <v>0.5101</v>
       </c>
       <c r="V2" t="n">
         <v>1.3252</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4742</v>
+        <v>1.9232</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8276</v>
+        <v>1.4924</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6466</v>
+        <v>0.4308</v>
       </c>
       <c r="G3" t="n">
         <v>0.0542</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3102</v>
+        <v>0.7592</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9542</v>
+        <v>0.6189</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3561</v>
+        <v>0.1403</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1952</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1985</v>
+        <v>1.3794</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6312</v>
+        <v>1.2522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4327</v>
+        <v>0.1271</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5795</v>
+        <v>-0.4351</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7603</v>
+        <v>-1.7396</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8192</v>
+        <v>1.3045</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3228</v>
+        <v>1.2807</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9395</v>
+        <v>-0.9577</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2622</v>
+        <v>2.2384</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9022</v>
+        <v>-1.7158</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1792</v>
+        <v>-0.7819</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0814</v>
+        <v>-0.9339</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5159</v>
+        <v>0.3794</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2882</v>
+        <v>0.1466</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2276</v>
+        <v>0.2328</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7156</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3629</v>
+        <v>0.7997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5132</v>
+        <v>1.7504</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1503</v>
+        <v>-0.9507</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4351</v>
+        <v>0.9288</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7396</v>
+        <v>1.4842</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3045</v>
+        <v>-0.5554</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2807</v>
+        <v>2.5131</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9577</v>
+        <v>1.9011</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2384</v>
+        <v>0.612</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7158</v>
+        <v>-1.5843</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7819</v>
+        <v>-0.4169</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9339</v>
+        <v>-1.1674</v>
       </c>
       <c r="P5" t="n">
         <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.637</v>
+        <v>-0.6294</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5924</v>
+        <v>-0.3929</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0446</v>
+        <v>-0.2364</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2234</v>
+        <v>-0.2984</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3899</v>
+        <v>0.8741</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1665</v>
+        <v>-1.1724</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9288</v>
+        <v>-1.5795</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4842</v>
+        <v>-0.7603</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5554</v>
+        <v>-0.8192</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5131</v>
+        <v>0.3228</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9011</v>
+        <v>-0.9395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.612</v>
+        <v>1.2622</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5843</v>
+        <v>-1.9022</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4169</v>
+        <v>0.1792</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1674</v>
+        <v>-2.0814</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2057</v>
+        <v>1.019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4522</v>
+        <v>0.4879</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3698</v>
+        <v>-0.3904</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3698</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3252</v>
+        <v>-1.0652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0839</v>
+        <v>-0.8102</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4091</v>
+        <v>-0.255</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0308</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8154</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1596</v>
+        <v>0.2656</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V7" t="n">
         <v>0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.806</v>
+        <v>-2.1235</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7898</v>
+        <v>-0.9254</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0162</v>
+        <v>-1.1981</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4603</v>
+        <v>-2.8748</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0316</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4287</v>
+        <v>-3.6687</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3789</v>
+        <v>-1.4881</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4171</v>
+        <v>1.0132</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>-2.5013</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0814</v>
+        <v>-1.3867</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.2193</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.467</v>
+        <v>-1.1674</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2381</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>-0.2824</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1729</v>
+        <v>-0.2262</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7602</v>
+        <v>1.695</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.0202</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7602</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1767</v>
+        <v>-2.6566</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5779</v>
+        <v>-1.6096</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5988</v>
+        <v>-1.047</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8748</v>
+        <v>-2.4603</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7939000000000001</v>
+        <v>-2.0316</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6687</v>
+        <v>-0.4287</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4881</v>
+        <v>-1.3789</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0132</v>
+        <v>-1.4171</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.5013</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3867</v>
+        <v>-1.0814</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2193</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1674</v>
+        <v>-0.467</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5618</v>
+        <v>-0.0886</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9349</v>
+        <v>-0.2307</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6269</v>
+        <v>0.1421</v>
       </c>
       <c r="V9" t="n">
-        <v>1.695</v>
+        <v>-0.7602</v>
       </c>
       <c r="W9" t="n">
-        <v>3.0202</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3252</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0429</v>
+        <v>-3.9551</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7544</v>
+        <v>-2.5741</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2885</v>
+        <v>-1.381</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3047</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7382</v>
+        <v>-0.6504</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.4362</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1217</v>
+        <v>-0.2142</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7426</v>
+        <v>-4.2492</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.2462</v>
+        <v>-5.2152</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5036</v>
+        <v>0.966</v>
       </c>
       <c r="G11" t="n">
         <v>-6.3062</v>
@@ -1312,13 +1312,13 @@
         <v>2.8276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1542</v>
+        <v>0.3392</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9349</v>
+        <v>0.0961</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2193</v>
+        <v>0.243</v>
       </c>
       <c r="V11" t="n">
         <v>0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.949899999999999</v>
+        <v>-3.9225</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.765599999999999</v>
+        <v>-0.7382</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1843</v>
+        <v>-3.184299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-12.0405</v>
@@ -1381,22 +1381,22 @@
         <v>-11.6741</v>
       </c>
       <c r="P12" t="n">
-        <v>5.4376</v>
+        <v>5.437600000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.787699999999999</v>
+        <v>-9.787700000000001</v>
       </c>
       <c r="R12" t="n">
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5227999999999997</v>
+        <v>1.5502</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3665000000000002</v>
+        <v>0.6610999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8892000000000002</v>
+        <v>0.8892000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
@@ -1405,13 +1405,13 @@
         <v>6.821199999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.691199999999999</v>
+        <v>-5.6912</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1332</v>
+        <v>4.5426</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9826</v>
+        <v>2.4687</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1505</v>
+        <v>2.0739</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5553</v>
+        <v>2.4657</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3504</v>
+        <v>0.4561</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2049</v>
+        <v>2.0097</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2679</v>
+        <v>2.0803</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8527</v>
+        <v>0.6268</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4152</v>
+        <v>1.4535</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2874</v>
+        <v>0.3854</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5022</v>
+        <v>-0.1707</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7897</v>
+        <v>0.5562</v>
       </c>
       <c r="P13" t="n">
         <v>-0.6525</v>
@@ -1468,22 +1468,22 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9699</v>
+        <v>-0.0955</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8468</v>
+        <v>-0.2391</v>
       </c>
       <c r="U13" t="n">
-        <v>0.123</v>
+        <v>0.1436</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7395</v>
+        <v>2.8249</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7395</v>
+        <v>3.0202</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8059</v>
+        <v>3.9292</v>
       </c>
       <c r="E14" t="n">
         <v>4.7654</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9594</v>
+        <v>-0.8361</v>
       </c>
       <c r="G14" t="n">
         <v>4.1244</v>
@@ -1546,13 +1546,13 @@
         <v>0.435</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5583</v>
+        <v>-0.435</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2158</v>
+        <v>-0.0925</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1952</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6241</v>
+        <v>3.4311</v>
       </c>
       <c r="E15" t="n">
-        <v>1.91</v>
+        <v>0.8592</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7142</v>
+        <v>2.5718</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4657</v>
+        <v>3.5553</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4561</v>
+        <v>1.3504</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0097</v>
+        <v>2.2049</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0803</v>
+        <v>3.2679</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6268</v>
+        <v>1.8527</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4535</v>
+        <v>1.4152</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3854</v>
+        <v>0.2874</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1707</v>
+        <v>-0.5022</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5562</v>
+        <v>0.7897</v>
       </c>
       <c r="P15" t="n">
         <v>-0.6525</v>
@@ -1624,28 +1624,28 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.014</v>
+        <v>1.2678</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.7234</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2161</v>
+        <v>0.5444</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8249</v>
+        <v>-0.7395</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0202</v>
+        <v>-0.7395</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5871</v>
+        <v>1.1565</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2781</v>
+        <v>1.2787</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8653</v>
+        <v>-0.1222</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9350000000000001</v>
+        <v>3.0495</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1527</v>
+        <v>-1.134</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0878</v>
+        <v>4.1835</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2204</v>
+        <v>3.6736</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6538</v>
+        <v>-0.4007</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8742</v>
+        <v>4.0744</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2854</v>
+        <v>-0.6241</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4989</v>
+        <v>-0.7333</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2136</v>
+        <v>0.1091</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1524</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.411</v>
+        <v>-0.0024</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5633</v>
+        <v>0.5221</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3698</v>
+        <v>-1.3252</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3698</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3729</v>
+        <v>0.6373</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6081</v>
+        <v>-0.1663</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2353</v>
+        <v>0.8036</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0495</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.134</v>
+        <v>-1.1527</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1835</v>
+        <v>2.0878</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6736</v>
+        <v>1.2204</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4007</v>
+        <v>-0.6538</v>
       </c>
       <c r="L17" t="n">
-        <v>4.0744</v>
+        <v>1.8742</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6241</v>
+        <v>-0.2854</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7333</v>
+        <v>-0.4989</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1091</v>
+        <v>0.2136</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.3926</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2639</v>
+        <v>0.2025</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.2992</v>
       </c>
       <c r="U17" t="n">
-        <v>0.409</v>
+        <v>0.5017</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3252</v>
+        <v>0.3698</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3252</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2063</v>
+        <v>0.4706</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6596</v>
+        <v>-0.1008</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4533</v>
+        <v>0.5715</v>
       </c>
       <c r="G18" t="n">
         <v>0.3006</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5721000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.1826</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1693</v>
+        <v>0.2875</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.222</v>
+        <v>-0.5816</v>
       </c>
       <c r="E19" t="n">
-        <v>0.63</v>
+        <v>0.183</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.852</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.7931</v>
@@ -1936,13 +1936,13 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4624</v>
+        <v>0.1027</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4146</v>
+        <v>-0.0324</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0478</v>
+        <v>0.1352</v>
       </c>
       <c r="V19" t="n">
         <v>-1.695</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5481</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0368</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5113</v>
+        <v>-0.6038</v>
       </c>
       <c r="G20" t="n">
         <v>0.6131</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2912</v>
+        <v>-0.3836</v>
       </c>
       <c r="T20" t="n">
         <v>-0.125</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1662</v>
+        <v>-0.2587</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8457</v>
+        <v>-0.8149</v>
       </c>
       <c r="E21" t="n">
         <v>0.4972</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3429</v>
+        <v>-1.3121</v>
       </c>
       <c r="G21" t="n">
         <v>0.3322</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0479</v>
+        <v>-0.0171</v>
       </c>
       <c r="T21" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5962</v>
+        <v>-2.3778</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7484</v>
+        <v>-2.5249</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1522</v>
+        <v>0.1471</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6438</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7348</v>
+        <v>-0.5164</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4675</v>
+        <v>-0.2439</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2674</v>
+        <v>-0.2725</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1551</v>
+        <v>-3.3124</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4862</v>
+        <v>-4.0392</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3311</v>
+        <v>0.7267</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4848</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6251</v>
+        <v>0.2175</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5239</v>
+        <v>-0.0769</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1012</v>
+        <v>0.2944</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.949799999999999</v>
+        <v>6.44</v>
       </c>
       <c r="E24" t="n">
-        <v>3.184199999999999</v>
+        <v>3.184199999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7657</v>
+        <v>3.255800000000001</v>
       </c>
       <c r="G24" t="n">
         <v>12.0403</v>
@@ -2326,13 +2326,13 @@
         <v>9.787800000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5226000000000003</v>
+        <v>0.9674000000000003</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8892000000000002</v>
+        <v>-0.8890999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3662000000000001</v>
+        <v>1.8566</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2341,7 +2341,7 @@
         <v>5.691299999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.821199999999999</v>
+        <v>-6.8212</v>
       </c>
     </row>
   </sheetData>
